--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484082_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484082_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8067</v>
+        <v>5.7692</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0881</v>
+        <v>6.2751</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2814</v>
+        <v>-0.5059</v>
       </c>
       <c r="G2" t="n">
         <v>3.1449</v>
@@ -610,13 +610,13 @@
         <v>2.3806</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.195</v>
+        <v>-0.2324</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4307</v>
+        <v>-0.2436</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2356</v>
+        <v>0.0112</v>
       </c>
       <c r="V2" t="n">
         <v>0.6745</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.415</v>
+        <v>3.0476</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4313</v>
+        <v>2.8394</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0162</v>
+        <v>0.2082</v>
       </c>
       <c r="G3" t="n">
         <v>2.067</v>
@@ -688,13 +688,13 @@
         <v>1.9838</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.6358</v>
+        <v>-1.0033</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7368</v>
+        <v>-0.3287</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.899</v>
+        <v>-0.6746</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0791</v>
+        <v>3.0452</v>
       </c>
       <c r="E4" t="n">
-        <v>2.514</v>
+        <v>3.1715</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4349</v>
+        <v>-0.1263</v>
       </c>
       <c r="G4" t="n">
         <v>-1.0242</v>
@@ -766,13 +766,13 @@
         <v>1.7855</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2339</v>
+        <v>-0.2678</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9125</v>
+        <v>-0.255</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3215</v>
+        <v>-0.0129</v>
       </c>
       <c r="V4" t="n">
         <v>2.7502</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. POU BLINNIKOV</t>
+          <t>A. IDDRISU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1422</v>
+        <v>0.4517</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0645</v>
+        <v>-0.2288</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0777</v>
+        <v>0.6804</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0484</v>
+        <v>-0.3437</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2598</v>
+        <v>0.0605</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.2113</v>
+        <v>-0.4042</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0207</v>
+        <v>0.1056</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5779</v>
+        <v>-0.0149</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5572</v>
+        <v>0.1205</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9723000000000001</v>
+        <v>-0.4493</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3181</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6542</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1903</v>
+        <v>1.1903</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7855</v>
+        <v>1.1903</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1489</v>
+        <v>-0.8035</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8843</v>
+        <v>-0.3344</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2646</v>
+        <v>-0.4691</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1352</v>
+        <v>0.4085</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1352</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.4085</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. IDDRISU</t>
+          <t>D. POU BLINNIKOV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4338</v>
+        <v>0.2838</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3308</v>
+        <v>-0.4853</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7645999999999999</v>
+        <v>0.7691</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3437</v>
+        <v>0.0484</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0605</v>
+        <v>1.2598</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4042</v>
+        <v>-1.2113</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1056</v>
+        <v>1.0207</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0149</v>
+        <v>1.5779</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1205</v>
+        <v>-0.5572</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4493</v>
+        <v>-0.9723000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>0.07530000000000001</v>
+        <v>-0.3181</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.6542</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1903</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q6" t="n">
+        <v>-2.9758</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.7855</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.2905</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.1352</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.1352</v>
+      </c>
+      <c r="X6" t="n">
         <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.1903</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-0.8213</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-0.4364</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-0.3849</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.4085</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.4085</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5494</v>
+        <v>-0.6747</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1829</v>
+        <v>-0.3643</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3665</v>
+        <v>-0.3104</v>
       </c>
       <c r="G7" t="n">
         <v>0.1605</v>
@@ -1000,13 +1000,13 @@
         <v>1.7855</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.2239</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0566</v>
+        <v>-0.238</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.042</v>
+        <v>0.0141</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2065</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.627</v>
+        <v>-1.194</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8723</v>
+        <v>-0.2148</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7547</v>
+        <v>-0.9792</v>
       </c>
       <c r="G8" t="n">
         <v>1.5037</v>
@@ -1078,13 +1078,13 @@
         <v>2.1822</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1983</v>
+        <v>-0.7652</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3602</v>
+        <v>-0.7027</v>
       </c>
       <c r="U8" t="n">
-        <v>0.162</v>
+        <v>-0.0625</v>
       </c>
       <c r="V8" t="n">
         <v>-0.9405</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9152</v>
+        <v>-1.3955</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9285</v>
+        <v>-1.577</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0132</v>
+        <v>0.1816</v>
       </c>
       <c r="G9" t="n">
         <v>-1.2238</v>
@@ -1156,13 +1156,13 @@
         <v>2.9758</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0044</v>
+        <v>-0.4846</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8047</v>
+        <v>-0.4533</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1997</v>
+        <v>-0.0313</v>
       </c>
       <c r="V9" t="n">
         <v>-1.4724</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. BRADLEY MAYOL</t>
+          <t>A. BENNASAR ROJO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0441</v>
+        <v>-2.9917</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.168</v>
+        <v>-2.225</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8762</v>
+        <v>-0.7667</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.9306</v>
+        <v>-2.0905</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7566000000000001</v>
+        <v>-0.4283</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.1741</v>
+        <v>-1.6622</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2895</v>
+        <v>-0.9723000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1008</v>
+        <v>-0.3725</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3903</v>
+        <v>-0.5999</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6411</v>
+        <v>-1.1181</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.0558</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7837</v>
+        <v>-1.0623</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9919</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9838</v>
+        <v>0.7935</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8394</v>
+        <v>-0.7029</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1135</v>
+        <v>-0.2607</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9529</v>
+        <v>-0.4422</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. BENNASAR ROJO</t>
+          <t>J. BRADLEY MAYOL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1561</v>
+        <v>-3.5098</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3893</v>
+        <v>-2.7178</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7667</v>
+        <v>-0.792</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0905</v>
+        <v>-2.9306</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4283</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.6622</v>
+        <v>-2.1741</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9723000000000001</v>
+        <v>-1.2895</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3725</v>
+        <v>0.1008</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5999</v>
+        <v>-1.3903</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1181</v>
+        <v>-1.6411</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0558</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0623</v>
+        <v>-0.7837</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1984</v>
+        <v>0.9919</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7935</v>
+        <v>1.9838</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8672</v>
+        <v>-1.3051</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4251</v>
+        <v>-0.4363</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4422</v>
+        <v>-0.8687</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="12">
@@ -1345,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.585000000000001</v>
+        <v>2.831800000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>3.226099999999998</v>
+        <v>4.473000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6411</v>
+        <v>-1.6412</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6882999999999995</v>
+        <v>-0.6883000000000004</v>
       </c>
       <c r="H12" t="n">
-        <v>6.826300000000001</v>
+        <v>6.826299999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-7.514700000000001</v>
+        <v>-7.5147</v>
       </c>
       <c r="J12" t="n">
         <v>10.6742</v>
@@ -1369,7 +1369,7 @@
         <v>11.6467</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.9727</v>
+        <v>-0.9726999999999998</v>
       </c>
       <c r="M12" t="n">
         <v>-11.3626</v>
@@ -1381,7 +1381,7 @@
         <v>-6.542</v>
       </c>
       <c r="P12" t="n">
-        <v>7.935399999999999</v>
+        <v>7.9354</v>
       </c>
       <c r="Q12" t="n">
         <v>-10.9111</v>
@@ -1390,10 +1390,10 @@
         <v>18.8465</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.745000000000001</v>
+        <v>-5.498199999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.1652</v>
+        <v>-2.9182</v>
       </c>
       <c r="U12" t="n">
         <v>-2.58</v>
@@ -1402,7 +1402,7 @@
         <v>1.083</v>
       </c>
       <c r="W12" t="n">
-        <v>7.628299999999999</v>
+        <v>7.6283</v>
       </c>
       <c r="X12" t="n">
         <v>-6.545199999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.6543</v>
+        <v>5.6278</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0132</v>
+        <v>3.1356</v>
       </c>
       <c r="F13" t="n">
-        <v>2.641</v>
+        <v>2.4923</v>
       </c>
       <c r="G13" t="n">
         <v>3.692</v>
@@ -1468,13 +1468,13 @@
         <v>1.7855</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0254</v>
+        <v>0.999</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2469</v>
+        <v>-0.1246</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2723</v>
+        <v>1.1236</v>
       </c>
       <c r="V13" t="n">
         <v>1.1352</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. BORRERO PERLAZA</t>
+          <t>P. PARISI TRIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7585</v>
+        <v>4.2522</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0406</v>
+        <v>6.0006</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2821</v>
+        <v>-1.7484</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4811</v>
+        <v>2.4049</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1388</v>
+        <v>-0.181</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3423</v>
+        <v>2.5859</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1846</v>
+        <v>3.0986</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9436</v>
+        <v>0.6812</v>
       </c>
       <c r="L14" t="n">
-        <v>0.241</v>
+        <v>2.4174</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7035</v>
+        <v>-0.6937</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.8048</v>
+        <v>-0.8623</v>
       </c>
       <c r="O14" t="n">
-        <v>1.1013</v>
+        <v>0.1685</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3968</v>
+        <v>0.3968</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R14" t="n">
-        <v>0.5952</v>
+        <v>1.3887</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5433</v>
+        <v>1.1846</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8479</v>
+        <v>0.3458</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6954</v>
+        <v>0.8388</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.8692</v>
+        <v>0.266</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.5481</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.8692</v>
+        <v>-3.2821</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. PARISI TRIA</t>
+          <t>B. BORRERO PERLAZA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2081</v>
+        <v>2.7441</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9803</v>
+        <v>2.9183</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7722</v>
+        <v>-0.1741</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4049</v>
+        <v>2.4811</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.181</v>
+        <v>1.1388</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5859</v>
+        <v>1.3423</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0986</v>
+        <v>3.1846</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6812</v>
+        <v>2.9436</v>
       </c>
       <c r="L15" t="n">
-        <v>2.4174</v>
+        <v>0.241</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6937</v>
+        <v>-0.7035</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8623</v>
+        <v>-1.8048</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1685</v>
+        <v>1.1013</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3968</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3887</v>
+        <v>0.5952</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1405</v>
+        <v>1.529</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6744</v>
+        <v>0.7256</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8034</v>
       </c>
       <c r="V15" t="n">
-        <v>0.266</v>
+        <v>-0.8692</v>
       </c>
       <c r="W15" t="n">
-        <v>3.5481</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-3.2821</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. DIAZ SANCHEZ</t>
+          <t>P. MARRÓN ROSA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3897</v>
+        <v>2.0372</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3832</v>
+        <v>2.0619</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0065</v>
+        <v>-0.0248</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.6208</v>
+        <v>0.8204</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1413</v>
+        <v>0.9329</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.4795</v>
+        <v>-0.1126</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4387</v>
+        <v>1.6485</v>
       </c>
       <c r="K16" t="n">
-        <v>0.121</v>
+        <v>1.528</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5597</v>
+        <v>0.1205</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1821</v>
+        <v>-0.8280999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2623</v>
+        <v>-0.5951</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9198</v>
+        <v>-0.2331</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9919</v>
+        <v>0.5952</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9919</v>
+        <v>0.5952</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8121</v>
+        <v>0.3557</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6155</v>
+        <v>0.1475</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1966</v>
+        <v>0.2082</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2065</v>
+        <v>0.266</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2065</v>
+        <v>0.266</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1036</v>
+        <v>1.8111</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6802</v>
+        <v>2.4762</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5766</v>
+        <v>-0.665</v>
       </c>
       <c r="G17" t="n">
         <v>0.0086</v>
@@ -1780,13 +1780,13 @@
         <v>0.9919</v>
       </c>
       <c r="S17" t="n">
-        <v>1.103</v>
+        <v>0.8106</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5613</v>
+        <v>0.3572</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5417999999999999</v>
+        <v>0.4534</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. MARRÓN ROSA</t>
+          <t>R. DIAZ SANCHEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5245</v>
+        <v>1.6475</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8579</v>
+        <v>1.669</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3334</v>
+        <v>-0.0216</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8204</v>
+        <v>-1.6208</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9329</v>
+        <v>-0.1413</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1126</v>
+        <v>-1.4795</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6485</v>
+        <v>-0.4387</v>
       </c>
       <c r="K18" t="n">
-        <v>1.528</v>
+        <v>0.121</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1205</v>
+        <v>-0.5597</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8280999999999999</v>
+        <v>-1.1821</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5951</v>
+        <v>-0.2623</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2331</v>
+        <v>-0.9198</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.157</v>
+        <v>1.0699</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0566</v>
+        <v>0.9013</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1004</v>
+        <v>0.1686</v>
       </c>
       <c r="V18" t="n">
-        <v>0.266</v>
+        <v>1.2065</v>
       </c>
       <c r="W18" t="n">
-        <v>0.266</v>
+        <v>1.2065</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6152</v>
+        <v>0.003</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2491</v>
+        <v>0.6369</v>
       </c>
       <c r="F19" t="n">
         <v>-0.6339</v>
@@ -1936,10 +1936,10 @@
         <v>0.9919</v>
       </c>
       <c r="S19" t="n">
-        <v>1.7799</v>
+        <v>1.1677</v>
       </c>
       <c r="T19" t="n">
-        <v>1.6042</v>
+        <v>0.992</v>
       </c>
       <c r="U19" t="n">
         <v>0.1757</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. VERANO FORES</t>
+          <t>A. QUIROS LOPEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6964</v>
+        <v>-0.6156</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6563</v>
+        <v>-0.7718</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0401</v>
+        <v>0.1562</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2571</v>
+        <v>-0.2401</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7158</v>
+        <v>0.3273</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9729</v>
+        <v>-0.5674</v>
       </c>
       <c r="J20" t="n">
-        <v>0.585</v>
+        <v>0.8666</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0202</v>
+        <v>0.7863</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5648</v>
+        <v>0.0803</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3279</v>
+        <v>-1.1067</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.736</v>
+        <v>-0.459</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4081</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7935</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1984</v>
+        <v>0.9919</v>
       </c>
       <c r="S20" t="n">
-        <v>0.106</v>
+        <v>0.2792</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2494</v>
+        <v>0.0794</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3554</v>
+        <v>0.1997</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.266</v>
+        <v>0.3373</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.266</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. QUIROS LOPEZ</t>
+          <t>R. VERANO FORES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7082000000000001</v>
+        <v>-0.6225000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3637</v>
+        <v>-0.5543</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3445</v>
+        <v>-0.0682</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2401</v>
+        <v>0.2571</v>
       </c>
       <c r="H21" t="n">
+        <v>-0.7158</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.9729</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.5648</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-0.3279</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-0.736</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.4081</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.7935</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.9919</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.1984</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.1474</v>
+      </c>
+      <c r="U21" t="n">
         <v>0.3273</v>
       </c>
-      <c r="I21" t="n">
-        <v>-0.5674</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.8666</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.7863</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.0803</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-1.1067</v>
-      </c>
-      <c r="N21" t="n">
-        <v>-0.459</v>
-      </c>
-      <c r="O21" t="n">
-        <v>-0.6477000000000001</v>
-      </c>
-      <c r="P21" t="n">
-        <v>-0.9919</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>-1.9838</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.9919</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.1865</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.4876</v>
-      </c>
-      <c r="U21" t="n">
-        <v>-0.301</v>
-      </c>
       <c r="V21" t="n">
-        <v>0.3373</v>
+        <v>-0.266</v>
       </c>
       <c r="W21" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.0713</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1037</v>
+        <v>-1.9456</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7987</v>
+        <v>-1.6966</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3051</v>
+        <v>-0.2489</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4132</v>
@@ -2170,13 +2170,13 @@
         <v>0.5952</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0873</v>
+        <v>0.0709</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.187</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0998</v>
+        <v>0.1559</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2065</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.2074</v>
+        <v>-5.7467</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.6534</v>
+        <v>-4.6331</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.554</v>
+        <v>-1.1135</v>
       </c>
       <c r="G23" t="n">
         <v>-2.7406</v>
@@ -2248,13 +2248,13 @@
         <v>1.1903</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4749</v>
+        <v>-0.0141</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.621</v>
+        <v>-0.6007</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1461</v>
+        <v>0.5865</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2065</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.122999999999999</v>
+        <v>-9.417199999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.8254</v>
+        <v>-9.335599999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2976</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-2.5304</v>
@@ -2326,13 +2326,13 @@
         <v>0.5952</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7675</v>
+        <v>0.4733</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4989</v>
+        <v>-0.0112</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2686</v>
+        <v>0.4845</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0118</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.5848</v>
+        <v>-0.2247000000000003</v>
       </c>
       <c r="E25" t="n">
-        <v>1.906999999999998</v>
+        <v>1.9071</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.492</v>
+        <v>-2.1315</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6883000000000004</v>
+        <v>0.6882999999999986</v>
       </c>
       <c r="H25" t="n">
         <v>-6.8264</v>
@@ -2404,13 +2404,13 @@
         <v>10.9113</v>
       </c>
       <c r="S25" t="n">
-        <v>6.745</v>
+        <v>8.1058</v>
       </c>
       <c r="T25" t="n">
-        <v>2.5801</v>
+        <v>2.5799</v>
       </c>
       <c r="U25" t="n">
-        <v>4.1653</v>
+        <v>5.5256</v>
       </c>
       <c r="V25" t="n">
         <v>-1.083</v>
